--- a/Data_clean/MCAS/Estados_US/Edos_USA_2023/NEW_HAMPSHIRE_2023.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2023/NEW_HAMPSHIRE_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CHAMULA</t>
+          <t>Chamula</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHENALHÓ</t>
+          <t>Chenalhó</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA TRINITARIA</t>
+          <t>La Trinitaria</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LAS MARGARITAS</t>
+          <t>Las Margaritas</t>
         </is>
       </c>
       <c r="C5">
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OCOTEPEC</t>
+          <t>Ocotepec</t>
         </is>
       </c>
       <c r="C6">
@@ -447,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SILTEPEC</t>
+          <t>Siltepec</t>
         </is>
       </c>
       <c r="C7">
@@ -460,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SOCOLTENANGO</t>
+          <t>Socoltenango</t>
         </is>
       </c>
       <c r="C8">
@@ -473,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TEOPISCA</t>
+          <t>Teopisca</t>
         </is>
       </c>
       <c r="C9">
@@ -486,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TUZANTÁN</t>
+          <t>Tuzantán</t>
         </is>
       </c>
       <c r="C10">
@@ -499,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C11">
@@ -514,12 +559,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JUÁREZ</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="C12">
@@ -530,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C13">
@@ -545,12 +595,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C14">
@@ -561,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C15">
@@ -574,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C16">
@@ -587,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C17">
@@ -602,12 +667,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLIMA</t>
+          <t>Colima</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MANZANILLO</t>
+          <t>Manzanillo</t>
         </is>
       </c>
       <c r="C18">
@@ -618,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VILLA DE ÁLVAREZ</t>
+          <t>Villa De Álvarez</t>
         </is>
       </c>
       <c r="C19">
@@ -631,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C20">
@@ -646,12 +721,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VICENTE GUERRERO</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C21">
@@ -662,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C22">
@@ -677,12 +757,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TENANGO DEL VALLE</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C23">
@@ -693,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA DE BAZ</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C24">
@@ -706,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C25">
@@ -721,12 +811,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CELAYA</t>
+          <t>Celaya</t>
         </is>
       </c>
       <c r="C26">
@@ -737,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CORTAZAR</t>
+          <t>Cortazar</t>
         </is>
       </c>
       <c r="C27">
@@ -750,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C28">
@@ -765,12 +865,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATLAMAJALCINGO DEL MONTE</t>
+          <t>Atlamajalcingo Del Monte</t>
         </is>
       </c>
       <c r="C29">
@@ -781,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CUALÁC</t>
+          <t>Cualác</t>
         </is>
       </c>
       <c r="C30">
@@ -794,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA UNIÓN DE ISIDORO MONTES DE OCA</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C31">
@@ -807,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SAN LUIS ACATLÁN</t>
+          <t>San Luis Acatlán</t>
         </is>
       </c>
       <c r="C32">
@@ -820,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ZAPOTITLÁN TABLAS</t>
+          <t>Zapotitlán Tablas</t>
         </is>
       </c>
       <c r="C33">
@@ -833,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C34">
@@ -848,12 +973,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AUTLÁN DE NAVARRO</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C35">
@@ -864,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CUAUTITLÁN DE GARCÍA BARRAGÁN</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C36">
@@ -877,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CUQUÍO</t>
+          <t>Cuquío</t>
         </is>
       </c>
       <c r="C37">
@@ -890,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DEGOLLADO</t>
+          <t>Degollado</t>
         </is>
       </c>
       <c r="C38">
@@ -903,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C39">
@@ -916,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C40">
@@ -931,12 +1081,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COALCOMÁN DE VÁZQUEZ PALLARES</t>
+          <t>Coalcomán De Vázquez Pallares</t>
         </is>
       </c>
       <c r="C41">
@@ -947,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IRIMBO</t>
+          <t>Irimbo</t>
         </is>
       </c>
       <c r="C42">
@@ -960,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LA PIEDAD</t>
+          <t>La Piedad</t>
         </is>
       </c>
       <c r="C43">
@@ -973,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LÁZARO CÁRDENAS</t>
+          <t>Lázaro Cárdenas</t>
         </is>
       </c>
       <c r="C44">
@@ -986,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PÁTZCUARO</t>
+          <t>Pátzcuaro</t>
         </is>
       </c>
       <c r="C45">
@@ -999,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZACAPU</t>
+          <t>Zacapu</t>
         </is>
       </c>
       <c r="C46">
@@ -1012,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47">
@@ -1027,12 +1207,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EL ESPINAL</t>
+          <t>El Espinal</t>
         </is>
       </c>
       <c r="C48">
@@ -1043,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HUAJUAPAN DE LEÓN</t>
+          <t>Huajuapan De León</t>
         </is>
       </c>
       <c r="C49">
@@ -1056,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SAN AGUSTÍN LOXICHA</t>
+          <t>San Agustín Loxicha</t>
         </is>
       </c>
       <c r="C50">
@@ -1069,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAN ANTONINO MONTE VERDE</t>
+          <t>San Antonino Monte Verde</t>
         </is>
       </c>
       <c r="C51">
@@ -1082,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SAN BALTAZAR LOXICHA</t>
+          <t>San Baltazar Loxicha</t>
         </is>
       </c>
       <c r="C52">
@@ -1095,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SANTA CATARINA LOXICHA</t>
+          <t>Santa Catarina Loxicha</t>
         </is>
       </c>
       <c r="C53">
@@ -1108,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE MORELOS</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C54">
@@ -1121,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C55">
@@ -1136,12 +1351,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ATLIXCO</t>
+          <t>Atlixco</t>
         </is>
       </c>
       <c r="C56">
@@ -1152,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C57">
@@ -1165,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TEZIUTLÁN</t>
+          <t>Teziutlán</t>
         </is>
       </c>
       <c r="C58">
@@ -1178,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C59">
@@ -1193,12 +1423,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EL MARQUÉS</t>
+          <t>El Marqués</t>
         </is>
       </c>
       <c r="C60">
@@ -1209,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LANDA DE MATAMOROS</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C61">
@@ -1222,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="C62">
@@ -1235,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C63">
@@ -1250,12 +1495,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUINTANA ROO</t>
+          <t>Quintana Roo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OTHÓN P. BLANCO</t>
+          <t>Othón P. Blanco</t>
         </is>
       </c>
       <c r="C64">
@@ -1266,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C65">
@@ -1281,12 +1531,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CIUDAD VALLES</t>
+          <t>Ciudad Valles</t>
         </is>
       </c>
       <c r="C66">
@@ -1297,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C67">
@@ -1312,12 +1567,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SOMBRERETE</t>
+          <t>Sombrerete</t>
         </is>
       </c>
       <c r="C68">
@@ -1328,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C69">
@@ -1343,7 +1603,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C70">
@@ -1351,41 +1611,6 @@
       </c>
       <c r="D70">
         <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
